--- a/database/template_collection.xlsx
+++ b/database/template_collection.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Œuvres" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exemple" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Artworks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transcriptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Types" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Émotions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emotions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,10 +41,6 @@
     <font>
       <i val="1"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="FF000000"/>
     </font>
     <font>
       <b val="1"/>
@@ -80,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -92,8 +88,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,7 +463,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRACES — modèle de tableur pour verser une collection</t>
+          <t>TRACES — spreadsheet template for adding a collection</t>
         </is>
       </c>
     </row>
@@ -478,77 +473,77 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Remplissez la feuille « Œuvres » : une ligne par œuvre, à partir de la ligne 3.</t>
+          <t>1. Fill in the "Artworks" sheet: one row per artwork, starting at row 3.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   La ligne 1 explique chaque colonne, la ligne 2 contient les en-têtes : ne les modifiez pas.</t>
+          <t xml:space="preserve">   Row 1 explains each column and row 2 holds the column headers: do not change them.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Les colonnes à en-tête jaune sont obligatoires.</t>
+          <t xml:space="preserve">   Columns with a yellow header are required.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2. Laissez « Database ID » vide : TRACES attribue lui-même les identifiants.</t>
+          <t>2. Leave "Database ID" empty: TRACES assigns the IDs itself. Keep "Origin" spelled the same in every spreadsheet you import.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3. Écrivez les textes de chaque ligne dans UNE langue (français, néerlandais ou anglais), indiquée dans la colonne « Language ».</t>
+          <t>3. Write the texts of each row in ONE language (French, Dutch or English) and enter it in the "Language" column.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Les traductions dans les deux autres langues sont préparées par TRACES, puis vous sont envoyées pour relecture.</t>
+          <t xml:space="preserve">   The other two languages are prepared with DeepL, then reviewed by your team.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4. « Type of object », « Question » et « Emotions » reprennent les valeurs des feuilles « Types », « Questions » et « Émotions ».</t>
+          <t>4. "Type of object", "Question" and "Emotions" use the values of the "Types", "Questions" and "Emotions" sheets.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Plusieurs émotions : séparez-les par des virgules. Les libellés FR, NL ou EN sont acceptés.</t>
+          <t xml:space="preserve">   Several emotions: separate them with commas. French, Dutch and English labels are all accepted.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>5. « Media » : le nom exact des fichiers images ou vidéos, séparés par des virgules (la première image sert de vignette).</t>
+          <t>5. "Media": the exact names of the image or video files, separated by commas (the first image is the thumbnail).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>6. Feuille « Transcriptions » (facultative) : pour les objets qui portent un texte (lettre, document, inscription).</t>
+          <t>6. "Transcriptions" sheet (optional): for objects that carry a text (letter, document, inscription).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>7. La feuille « Exemple » montre une ligne remplie ; elle n’est pas importée.</t>
+          <t>7. The "Example" sheet shows a filled-in row; it is not imported.</t>
         </is>
       </c>
     </row>
@@ -558,7 +553,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Détails et formats des médias : database/README.md du dépôt TRACES.</t>
+          <t>Full guide, media formats and commands: database/README.md in the TRACES repository.</t>
         </is>
       </c>
     </row>
@@ -596,77 +591,77 @@
     <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>À laisser vide (attribué par TRACES).</t>
+          <t>Leave empty (assigned by TRACES).</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Numéro d’inventaire de l’objet dans votre musée.</t>
+          <t>Inventory number of the object in your museum.</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Nom de votre institution, identique sur toutes les lignes.</t>
+          <t>Name of your institution, identical on every row.</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Langue des textes de cette ligne : fr, nl ou en.</t>
+          <t>Language of the texts of this row: fr, nl or en.</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Catégorie de l’objet : une valeur de la feuille « Types ».</t>
+          <t>Category of the object: a value from the "Types" sheet.</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Date ou période : 1935, 1870-1880, ca. 1900, 19e siècle…</t>
+          <t>Date or period: 1935, 1870-1880, ca. 1900, 19th century…</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Titre de l’œuvre, tel qu’il sera affiché.</t>
+          <t>Title of the artwork, as it will be shown.</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Auteur, artiste ou fabricant, si connu.</t>
+          <t>Author, artist or maker, if known.</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Personnes liées à l’objet (modèle, destinataire…), si utile.</t>
+          <t>People related to the object (sitter, recipient…), if useful.</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Ville ou lieu de conservation de l’objet.</t>
+          <t>City or place where the object is kept.</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Mots-clés qui décrivent la forme ET le contenu, séparés par des virgules.</t>
+          <t>Keywords describing the shape AND the content, separated by commas.</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>Émotions associées (feuille « Émotions »), séparées par des virgules. 2 à 4 conseillées.</t>
+          <t>Emotions related to the object ("Emotions" sheet), separated by commas. 2 to 4 recommended.</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>Texte de présentation lu par le visiteur (3 à 8 phrases).</t>
+          <t>Text read by visitors (3 to 8 sentences).</t>
         </is>
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>Numéro de la question posée au visiteur après l’œuvre (feuille « Questions »).</t>
+          <t>Number of the question this artwork is linked to ("Questions" sheet).</t>
         </is>
       </c>
       <c r="O1" s="3" t="inlineStr">
         <is>
-          <t>Noms des fichiers images/vidéos, séparés par des virgules. La 1re image = vignette.</t>
+          <t>Image/video file names, separated by commas. The first image is the thumbnail. Avoid names already used in assets/.</t>
         </is>
       </c>
     </row>
@@ -792,77 +787,77 @@
     <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>À laisser vide (attribué par TRACES).</t>
+          <t>Leave empty (assigned by TRACES).</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Numéro d’inventaire de l’objet dans votre musée.</t>
+          <t>Inventory number of the object in your museum.</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Nom de votre institution, identique sur toutes les lignes.</t>
+          <t>Name of your institution, identical on every row.</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Langue des textes de cette ligne : fr, nl ou en.</t>
+          <t>Language of the texts of this row: fr, nl or en.</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Catégorie de l’objet : une valeur de la feuille « Types ».</t>
+          <t>Category of the object: a value from the "Types" sheet.</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Date ou période : 1935, 1870-1880, ca. 1900, 19e siècle…</t>
+          <t>Date or period: 1935, 1870-1880, ca. 1900, 19th century…</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Titre de l’œuvre, tel qu’il sera affiché.</t>
+          <t>Title of the artwork, as it will be shown.</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Auteur, artiste ou fabricant, si connu.</t>
+          <t>Author, artist or maker, if known.</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Personnes liées à l’objet (modèle, destinataire…), si utile.</t>
+          <t>People related to the object (sitter, recipient…), if useful.</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Ville ou lieu de conservation de l’objet.</t>
+          <t>City or place where the object is kept.</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Mots-clés qui décrivent la forme ET le contenu, séparés par des virgules.</t>
+          <t>Keywords describing the shape AND the content, separated by commas.</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>Émotions associées (feuille « Émotions »), séparées par des virgules. 2 à 4 conseillées.</t>
+          <t>Emotions related to the object ("Emotions" sheet), separated by commas. 2 to 4 recommended.</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>Texte de présentation lu par le visiteur (3 à 8 phrases).</t>
+          <t>Text read by visitors (3 to 8 sentences).</t>
         </is>
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>Numéro de la question posée au visiteur après l’œuvre (feuille « Questions »).</t>
+          <t>Number of the question this artwork is linked to ("Questions" sheet).</t>
         </is>
       </c>
       <c r="O1" s="3" t="inlineStr">
         <is>
-          <t>Noms des fichiers images/vidéos, séparés par des virgules. La 1re image = vignette.</t>
+          <t>Image/video file names, separated by commas. The first image is the thumbnail. Avoid names already used in assets/.</t>
         </is>
       </c>
     </row>
@@ -952,12 +947,12 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Musée de l’Exemple</t>
+          <t>Museum of Example</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -972,7 +967,7 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Ours en peluche</t>
+          <t>Teddy bear</t>
         </is>
       </c>
       <c r="H3" s="6" t="n"/>
@@ -984,7 +979,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>ours, peluche, jouet, tissu usé, enfance, doudou</t>
+          <t>teddy bear, plush, toy, worn fabric, childhood, comforter</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>Cet ours en peluche a accompagné un enfant montois pendant toute son enfance. Son pelage usé et son oreille recousue témoignent des années de câlins et de jeux.</t>
+          <t>This teddy bear went everywhere with a child from Mons throughout his childhood. Its worn fur and its sewn-up ear tell of years of cuddles and games.</t>
         </is>
       </c>
       <c r="N3" s="6" t="n">
@@ -1002,7 +997,7 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>INV_1987_042_face.jpg, INV_1987_042_dos.jpg</t>
+          <t>INV_1987_042_front.jpg, INV_1987_042_back.jpg</t>
         </is>
       </c>
     </row>
@@ -1029,42 +1024,42 @@
     <row r="1" ht="45" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>À laisser vide.</t>
+          <t>Leave empty.</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Numéro d’inventaire de l’objet (comme dans « Œuvres »).</t>
+          <t>Inventory number of the object (as in "Artworks").</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Texte écrit sur l’objet, recopié tel quel (orthographe d’origine).</t>
+          <t>Text written on the object, copied as is (original spelling).</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Explication de ce texte pour le visiteur, dans la langue de l’œuvre.</t>
+          <t>Explanation of this text for visitors, in the language of the artwork.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Database ID</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Museum ID</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Transcription</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -1091,22 +1086,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Type of object (à recopier)</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Type of object (copy this value)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
@@ -1673,24 +1668,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>N°</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>NL</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>EN</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1695,17 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>What about you? What was your childhood like? Was it happy, sad, boring? What is the first memory that comes to mind when you think about your childhood?</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
           <t>Et vous ? Comment était votre enfance ? Était-elle heureuse, triste, ennuyeuse ? Quel est le premier souvenir qui vous vient à l'esprit quand vous pensez à votre enfance ?</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>En jij? Hoe was jouw jeugd? Was die gelukkig, verdrietig, saai? Wat is de eerste herinnering die in je opkomt als je aan je jeugd denkt?</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>What about you? What was your childhood like? Was it happy, sad, boring? What is the first memory that comes to mind when you think about your childhood?</t>
         </is>
       </c>
     </row>
@@ -1720,17 +1715,17 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
+          <t>If you had a very limited space to store memories, what are 3 memories you would keep?</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
           <t>Si vous aviez un espace très limité pour conserver des souvenirs, quels sont les 3 souvenirs que vous garderiez ?</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Als je maar heel weinig ruimte had om herinneringen te bewaren, welke 3 herinneringen zou je dan bijhouden?</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>If you had a very limited space to store memories, what are 3 memories you would keep?</t>
         </is>
       </c>
     </row>
@@ -1740,17 +1735,17 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
+          <t>And you? Do you keep a special or symbolic object from your childhood inherited by your parents? Can you share it's story?</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
           <t>Et vous ? Conservez-vous un objet spécial ou symbolique de votre enfance, hérité de vos parents ? Pouvez-vous nous raconter son histoire ?</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>En jij? Bewaar je een speciaal of symbolisch voorwerp uit je jeugd dat je van je ouders hebt geërfd? Kun je het verhaal erachter vertellen?</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>And you? Do you keep a special or symbolic object from your childhood inherited by your parents? Can you share it's story?</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1755,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
+          <t>Do you have childhood memories of waking up at night because of a nightmare? Or what was a memorable pleasant dream you remember still?</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
           <t>Enfant, vous souvenez-vous de vous être réveillé la nuit à cause d'un cauchemar ? Ou au contraire, y a-t-il un rêve agréable et marquant dont vous vous souvenez encore ?</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Herinner je je dat je als kind 's nachts wakker werd door een nachtmerrie? Of is er integendeel een aangename droom die je altijd is bijgebleven?</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Do you have childhood memories of waking up at night because of a nightmare? Or what was a memorable pleasant dream you remember still?</t>
         </is>
       </c>
     </row>
@@ -1780,17 +1775,17 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>Did you have pets when you were a kid? What's your best childhood memory with a pet?</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>Aviez-vous des animaux de compagnie quand vous étiez enfant ? Quel est votre meilleur souvenir d'enfance avec un animal ?</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Had je als kind huisdieren? Wat is je beste jeugdherinnering met een huisdier?</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Did you have pets when you were a kid? What's your best childhood memory with a pet?</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1795,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
+          <t>What was your favorite game when you were a child?</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
           <t>Quel était votre jeu préféré quand vous étiez enfant ?</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Wat was je favoriete spelletje toen je klein was?</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>What was your favorite game when you were a child?</t>
         </is>
       </c>
     </row>
@@ -1820,17 +1815,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
+          <t>Do you have a childhood memory related to a letter, written, sent or received, that made an impression on you?  Can you share your story?</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
           <t>Avez-vous un souvenir d'enfance lié à une lettre — écrite, envoyée ou reçue — qui vous a marqué ? Pouvez-vous nous raconter votre histoire ?</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Heb je een jeugdherinnering aan een brief — geschreven, verstuurd of ontvangen — die indruk op je maakte? Kun je je verhaal vertellen?</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Do you have a childhood memory related to a letter, written, sent or received, that made an impression on you?  Can you share your story?</t>
         </is>
       </c>
     </row>
@@ -1840,17 +1835,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>Do you know why your parents choose your name? What's the story behind?</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>Savez-vous pourquoi vos parents ont choisi votre prénom ? Quelle est l'histoire derrière ce choix ?</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Weet je waarom je ouders jouw naam gekozen hebben? Wat is het verhaal erachter?</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Do you know why your parents choose your name? What's the story behind?</t>
         </is>
       </c>
     </row>
@@ -1860,17 +1855,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>Do you have a childhood memory linked to a special piece of clothes of yours or a uniform you were wearing when you were little ?</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>Avez-vous un souvenir d'enfance lié à un vêtement particulier ou à un uniforme que vous portiez quand vous étiez petit ?</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Heb je een jeugdherinnering aan een speciaal kledingstuk of een uniform dat je droeg toen je klein was?</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Do you have a childhood memory linked to a special piece of clothes of yours or a uniform you were wearing when you were little ?</t>
         </is>
       </c>
     </row>
@@ -1880,17 +1875,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>What's your best childhood memory linked with a celebration like Saint-Nicolas's day or christmas?</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
           <t>Quel est votre meilleur souvenir d'enfance lié à une fête comme la Saint-Nicolas ou Noël ?</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Wat is je beste jeugdherinnering aan een feest zoals Sinterklaas of Kerstmis?</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>What's your best childhood memory linked with a celebration like Saint-Nicolas's day or christmas?</t>
         </is>
       </c>
     </row>
@@ -1900,17 +1895,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
+          <t>What is the first memorable childhood memory related to reuniting with loved ones that comes to mind?</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
           <t>Quel est le premier souvenir d'enfance marquant, lié à des retrouvailles avec des êtres chers, qui vous vient à l'esprit ?</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Wat is de eerste onvergetelijke jeugdherinnering aan een hereniging met dierbaren die in je opkomt?</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>What is the first memorable childhood memory related to reuniting with loved ones that comes to mind?</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1915,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>And you, when you were a child and in need of being conforted or protected, did your parents or grandparents invoked a specific saint, relative or character, real or imaginary ? Did you have a protective figure? Who was it ?</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
           <t>Et vous, quand vous étiez enfant et que vous aviez besoin d'être réconforté ou protégé, vos parents ou grands-parents invoquaient-ils un saint, un proche ou un personnage particulier, réel ou imaginaire ? Aviez-vous une figure protectrice ? Qui était-ce ?</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>En jij, toen je als kind troost of bescherming nodig had, riepen je ouders of grootouders dan een specifieke heilige, een familielid of een figuur aan, echt of denkbeeldig? Had je een beschermfiguur? Wie was het?</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>And you, when you were a child and in need of being conforted or protected, did your parents or grandparents invoked a specific saint, relative or character, real or imaginary ? Did you have a protective figure? Who was it ?</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1949,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
